--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>definition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>examples</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -459,16 +459,21 @@
           <t>Uncertainty</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of Measurement, that characterizes the dispersion of values that could reasonably be attributed to the Measurand.</t>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>- When the quality of Accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the Measurement results. Because Accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -462,6 +462,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,31 +456,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGClimate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Process of assessing, by independent means, the quality of data products derived from system outputs.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- (1) CEOS/ISO:19159 [RD10]; (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (3) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (4) NIST [RD15]; (5) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]
+- RD10:SO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
+- RD15: Prokhorov, A. V., R. U. Datla, V. P. Zakharenkov, V. Privalsky, T. W. Humpherys, and V. I. Sapritsky, Spaceborne Optoelectronic Sensors and their Radiometric Calibration. Terms and Definitions. Part 1. Calibration Techniques, Ed. by A. C. Parr and L. K. Issaev, NIST Technical Note NISTIR 7203, March 2005
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,22 +468,19 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
+          <t>Process of assessing, by independent means, the quality of data products derived from system outputs.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+          <t>- (1) CEOS/ISO:19159 [RD10]; (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (3) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (4) NIST [RD15]; (5) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]
+- RD10:SO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
+- RD15: Prokhorov, A. V., R. U. Datla, V. P. Zakharenkov, V. Privalsky, T. W. Humpherys, and V. I. Sapritsky, Spaceborne Optoelectronic Sensors and their Radiometric Calibration. Terms and Definitions. Part 1. Calibration Techniques, Ed. by A. C. Parr and L. K. Issaev, NIST Technical Note NISTIR 7203, March 2005
 - [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
 - NESDIS Data Management Lexicon and Related Terms</t>
         </is>
@@ -521,7 +518,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,28 +533,57 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- ISO 19116:2004(E)</t>
+          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -566,50 +592,24 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Process of assessing, by independent means, the quality of data products derived from system outputs.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>- (1) CEOS/ISO:19159 [RD10]; (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (3) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (4) NIST [RD15]; (5) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]
-- RD10:SO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
-- RD15: Prokhorov, A. V., R. U. Datla, V. P. Zakharenkov, V. Privalsky, T. W. Humpherys, and V. I. Sapritsky, Spaceborne Optoelectronic Sensors and their Radiometric Calibration. Terms and Definitions. Part 1. Calibration Techniques, Ed. by A. C. Parr and L. K. Issaev, NIST Technical Note NISTIR 7203, March 2005
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
+          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
     </row>

--- a/exports/xlsx/terms_definition_4.xlsx
+++ b/exports/xlsx/terms_definition_4.xlsx
@@ -456,10 +456,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -468,15 +497,15 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Process of assessing, by independent means, the quality of data products derived from system outputs.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>- (1) CEOS/ISO:19159 [RD10]; (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (3) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (4) NIST [RD15]; (5) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]
 - RD10:SO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
@@ -486,13 +515,46 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>- core
 - to be approved
@@ -501,86 +563,31 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Provision of objective evidence that specified requirements have been fulfilled.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]; (3) CDRH [ [RD1](https://www.fda.gov/media/73141/download) ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- ISO 19116:2004(E)</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -592,24 +599,17 @@
 - WGClimate</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, generated by it or included in its data packets, comprising science and engineering data, and possibly ancillary data.</t>
+          <t>Data enhancing processing and utilization of remote sensing instrument data, collected via different processes or platforms, preferably georeferenced, and usable as independent datasets.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc) [Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DInstrument%2BData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>
